--- a/output/Data and Chart Outputs/ireland_eirgrid_system_data.xlsx
+++ b/output/Data and Chart Outputs/ireland_eirgrid_system_data.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,12 +64,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,6 +159,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Ireland (Republic) generation by source (EirGrid) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -179,7 +181,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="5E5E5E"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -207,7 +209,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -235,7 +237,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="EDA100"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -263,7 +265,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="EDA100"/>
+              <a:srgbClr val="2A78D6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -701,7 +703,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -716,7 +717,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -745,7 +745,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -805,7 +804,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B2" t="n">
@@ -822,7 +821,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B3" t="n">
@@ -839,7 +838,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B4" t="n">
@@ -856,24 +855,24 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B5" t="n">
         <v>1261.912</v>
       </c>
       <c r="C5" t="n">
-        <v>915.093</v>
+        <v>915.0929999999998</v>
       </c>
       <c r="D5" t="n">
-        <v>56.984</v>
+        <v>56.98399999999999</v>
       </c>
       <c r="E5" t="n">
         <v>83.536</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B6" t="n">
@@ -883,14 +882,14 @@
         <v>545.76</v>
       </c>
       <c r="D6" t="n">
-        <v>71.959</v>
+        <v>71.95899999999999</v>
       </c>
       <c r="E6" t="n">
         <v>32.695</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B7" t="n">
@@ -900,21 +899,21 @@
         <v>636.033</v>
       </c>
       <c r="D7" t="n">
-        <v>79.419</v>
+        <v>79.41899999999998</v>
       </c>
       <c r="E7" t="n">
         <v>13.233</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B8" t="n">
         <v>1410.606</v>
       </c>
       <c r="C8" t="n">
-        <v>568.679</v>
+        <v>568.6790000000001</v>
       </c>
       <c r="D8" t="n">
         <v>118.39</v>
@@ -924,14 +923,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B9" t="n">
         <v>1107.996</v>
       </c>
       <c r="C9" t="n">
-        <v>899.176</v>
+        <v>899.1760000000002</v>
       </c>
       <c r="D9" t="n">
         <v>103.495</v>
@@ -941,7 +940,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B10" t="n">
@@ -958,7 +957,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B11" t="n">
@@ -975,24 +974,24 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B12" t="n">
         <v>1734.688</v>
       </c>
       <c r="C12" t="n">
-        <v>868.966</v>
+        <v>868.9660000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>22.866</v>
+        <v>22.86600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>46.008</v>
+        <v>46.00799999999999</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B13" t="n">
@@ -1009,7 +1008,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B14" t="n">
@@ -1026,7 +1025,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B15" t="n">
@@ -1036,14 +1035,14 @@
         <v>1410.92</v>
       </c>
       <c r="D15" t="n">
-        <v>39.073</v>
+        <v>39.07300000000001</v>
       </c>
       <c r="E15" t="n">
         <v>71.482</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B16" t="n">
@@ -1053,21 +1052,21 @@
         <v>997.95</v>
       </c>
       <c r="D16" t="n">
-        <v>86.78</v>
+        <v>86.77999999999999</v>
       </c>
       <c r="E16" t="n">
         <v>40.898</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B17" t="n">
         <v>1512.069</v>
       </c>
       <c r="C17" t="n">
-        <v>759.2430000000001</v>
+        <v>759.2430000000002</v>
       </c>
       <c r="D17" t="n">
         <v>119.27</v>
@@ -1077,7 +1076,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B18" t="n">
@@ -1094,7 +1093,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B19" t="n">
@@ -1111,14 +1110,14 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B20" t="n">
         <v>1477.245</v>
       </c>
       <c r="C20" t="n">
-        <v>658.396</v>
+        <v>658.3960000000001</v>
       </c>
       <c r="D20" t="n">
         <v>155.292</v>
@@ -1128,7 +1127,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B21" t="n">
@@ -1145,24 +1144,24 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B22" t="n">
         <v>1118.265</v>
       </c>
       <c r="C22" t="n">
-        <v>921.101</v>
+        <v>921.1009999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>97.399</v>
+        <v>97.39900000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>50.534</v>
+        <v>50.53399999999999</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B23" t="n">
@@ -1179,7 +1178,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B24" t="n">
@@ -1196,7 +1195,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B25" t="n">
@@ -1213,7 +1212,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B26" t="n">
@@ -1226,11 +1225,11 @@
         <v>28.021</v>
       </c>
       <c r="E26" t="n">
-        <v>84.76900000000001</v>
+        <v>84.76900000000002</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B27" t="n">
@@ -1240,14 +1239,14 @@
         <v>1246.364</v>
       </c>
       <c r="D27" t="n">
-        <v>35.29</v>
+        <v>35.29000000000001</v>
       </c>
       <c r="E27" t="n">
         <v>103.311</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B28" t="n">
@@ -1260,11 +1259,11 @@
         <v>105.161</v>
       </c>
       <c r="E28" t="n">
-        <v>94.295</v>
+        <v>94.29500000000002</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B29" t="n">
@@ -1277,18 +1276,18 @@
         <v>163.134</v>
       </c>
       <c r="E29" t="n">
-        <v>69.062</v>
+        <v>69.06200000000001</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B30" t="n">
         <v>1208.447</v>
       </c>
       <c r="C30" t="n">
-        <v>786.203</v>
+        <v>786.2029999999999</v>
       </c>
       <c r="D30" t="n">
         <v>217.301</v>
@@ -1298,14 +1297,14 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B31" t="n">
         <v>1175.956</v>
       </c>
       <c r="C31" t="n">
-        <v>821.4060000000001</v>
+        <v>821.4060000000002</v>
       </c>
       <c r="D31" t="n">
         <v>219.491</v>
@@ -1315,7 +1314,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B32" t="n">
@@ -1328,11 +1327,11 @@
         <v>258.162</v>
       </c>
       <c r="E32" t="n">
-        <v>6.6</v>
+        <v>6.599999999999999</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B33" t="n">
@@ -1349,7 +1348,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B34" t="n">
